--- a/data/callings.xlsx
+++ b/data/callings.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2 HP/level • Sneak Attack</t>
+          <t>2 Vigor/level • Sneak Attack</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>4 HP/level • Rage</t>
+          <t>4 Vigor/level • Rage</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3 HP/level • Panache</t>
+          <t>3 Vigor/level • Panache</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3 HP/level • Mark Prey</t>
+          <t>3 Vigor/level • Mark Prey</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3 HP/level • Drilled</t>
+          <t>3 Vigor/level • Drilled</t>
         </is>
       </c>
     </row>
@@ -725,18 +725,19 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You become Trained in Stealth.
-You gain Sneak Attack: +1d6 precision damage vs. Off-Guard foes.
+You gain Sneak Attack:
++1d6 precision damage vs. Off-Guard foes.
 Rises to +2d6 at Expert rank, +3d6 at Master, +4d6 at Legendary.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -749,26 +750,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Sneak Attack</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>In the first round, foes that haven't acted yet are Wrong-Footed to you.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Opportunist ↺</t>
+          <t>Opportunist ❶↺</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -776,22 +777,43 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sneak Attack</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Trigger An ally Hits a creature within your reach.
-Effect Strike that creature. It is Off-Guard to this Strike. Once per round.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> An ally Hits a creature within your reach.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Strike that creature. It is Off-Guard to this Strike.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -804,21 +826,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sneak Attack</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Once per turn, when your Sneak Attack damage applies to a Hit, the Zone it landed on becomes Exposed.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>Once per round, when your Sneak Attack damage applies to a Hit, the Zone it landed on becomes Exposed.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -831,21 +853,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sneak Attack</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>When your Sneak Attack damage applies, the target also takes 1d4 persistent bleed damage. This rises to 1d6 at Expert rank, 1d8 at Master, and 1d10 at Legendary.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -858,21 +880,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sneak Attack</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Whenever your Strike is a critical hit and deals damage, the target is Wrong-Footed against your attacks until the end of your next turn.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Whenever your Strike is a critical hit and deals damage, the target is Wrong-Footed against your attacks until the end of the next round.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -949,7 +971,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rage ◆</t>
+          <t>Rage ❶</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -962,27 +984,52 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>You become Trained in Athletics.
+          <r>
+            <t xml:space="preserve">You become Trained in Athletics.
 You gain the Rage action:
-Rage ◆  Duration 10 rounds
-You gain Temp HP = level + Might, +2 melee damage, −1 Evade. While raging, you are Heedless.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Rage ❶</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Duration</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> 10 rounds
+You gain Temporary Vigor = level + Might, +2 melee damage, −1 Evade. While raging, you are Heedless.
 Afterward, you're fatigued until you spend three actions to catch your breath.
 You may end your Rage as a free action, becoming fatigued as though it had run its course.
 Damage bonus rises to +4 melee damage at Expert rank, +6 at Master, +8 at Legendary.</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          </r>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sudden Charge ◆◆</t>
+          <t>Sudden Charge ❷</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -990,23 +1037,36 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Rage</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>You gain Sudden Charge:
-Sudden Charge ◆◆
-Stride twice, then Strike.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <r>
+            <t xml:space="preserve">You gain Sudden Charge:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Sudden Charge ❷</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Move twice, then Quick Strike. Your Moves may provoke Intercepts as normal.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1019,21 +1079,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Rage</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>While you are Raging, every Zone on you has +1 Protection, including Zones with no armor at all. An Exposed Zone still counts as 0.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1046,21 +1106,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Rage</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>When your Strike drops a creature while you are Raging, your Rage's remaining duration resets to 10 rounds.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1073,26 +1133,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Rage</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>You ignore the Fatigued condition while Raging, and when your Rage ends you need to spend only 1 action to catch your breath rather than 3.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Moment of Clarity ◇</t>
+          <t>Moment of Clarity ⓿</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1100,18 +1160,28 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Rage</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Frequency once per encounter
-You push back your rage for a moment in order to think clearly. Until the end of this turn, you lose your Heedless condition.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Frequency</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> once per encounter
+You push back your rage for a moment in order to think clearly. Until the end of this round, you lose your Heedless condition.</t>
+          </r>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1119,7 +1189,7 @@
           <t>Presence</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1209,25 +1279,25 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You become Trained in Acrobatics.
 You gain Panache whenever you critically succeed on a Strike, or when you successfully Feint or Demoralize.
 You can hold one Panache at a time and you keep it until you spend it or the encounter ends (whichever happens first).
-While you have Panache you gain a +1 circumstance bonus to Evade and a +5-foot circumstance bonus to your Speeds. At Expert rank, the Speed bonus increases to 10 feet. At Master rank, your Evade bonus increases to +2. At Legendary rank, your Speed bonus increases to 15 feet.
+While you have Panache you gain a +1 Situation bonus to Evade and a +1-foot Situation bonus to your Speeds. At Expert rank, Speed bonus increases to 2 feet. At Master rank, your Evade bonus increases to +2. At Legendary rank, your Speed bonus increases to 3 feet.
 Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Finisher ◆</t>
+          <t>Finisher ❶</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1235,29 +1305,53 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Spend your Panache and Strike, with the following effects:
-Hit add 2d6 precision damage.
-Graze add 1d6 precision damage.
+          <r>
+            <t xml:space="preserve">Spend your Panache and Strike, with the following effects:
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Hit</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> add 2d6 precision damage.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Graze</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> add 1d6 precision damage.
 You lose the Panache either way.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          </r>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Opportune Parry ↺</t>
+          <t>Opportune Parry ⓿↺</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1265,22 +1359,43 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Trigger A creature Grazes or Misses you while you have Panache.
-Effect You do not pay the Graze cost.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> A creature's Strike against you is Stopped (a Graze or a Miss) while you have Panache.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You take Control of the attacking weapon as though you had Parried, without spending an action.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1293,21 +1408,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>While you have Panache, you may Recenter as a free action once per turn.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>While you have Panache, you may Recenter ⓿ once per round.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1320,21 +1435,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>You begin every encounter with Panache if you are not surprised.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1347,27 +1462,27 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>When you Raise a Shield ◆ to gain a circumstance bonus to Guard from a buckler, increase the bonus from +1 to +2.
-While you have a buckler raised, if a creature critically misses you with a Strike, you gain Panache.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>When you Raise a Shield ❶ to gain a Situation bonus to Guard from a buckler, increase the bonus from +1 to +2.
+While you have a buckler raised, if a creature critically misses you with a Strike, you gain panache.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Extravagant Parry ◆</t>
+          <t>Extravagant Parry ❶</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1375,22 +1490,32 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Requirements You're wielding one or more one-handed weapons.
-You gain a +1 circumstance bonus to Guard until the start of your next turn, or a +2 circumstance bonus if you have a free hand or are wielding a weapon with the Parry trait. You lose this circumstance bonus if you no longer meet this talent's requirement. If a creature misses you with a Strike while you have this bonus, you gain Panache.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Requirements</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> You're wielding one or more one-handed weapons
+You gain a +1 Situation bonus to Guard until your next Opportunity, or a +2 Situation bonus if you have a free hand or are wielding a weapon with the parry trait. You lose this Situation bonus if you no longer meet this feat's requirement. If a creature misses you with a Strike while you have this bonus, you gain panache.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1467,7 +1592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mark Prey ◆</t>
+          <t>Mark Prey ❶</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1480,9 +1605,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You become Trained in Awareness.
@@ -1491,8 +1616,8 @@
 Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,21 +1630,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Mark Prey</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>You may Mark Prey as part of a Stride rather than spending an action.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>You may Mark Prey as part of a Move rather than spending an action.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,21 +1657,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Mark Prey</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>The first time each encounter your prey attacks you, you learn if its Evade or Guard is higher.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1559,26 +1684,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mark Prey</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>When you Hit your prey with the first Strike of your turn, its Speed is reduced by 10 feet until the end of its next turn.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>When you Hit your prey with the first Strike of the round, its Speed is reduced by 2 feet until the end of the next round.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>No Escape ↺</t>
+          <t>No Escape ❶↺</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1586,27 +1711,48 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mark Prey</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Trigger Your prey Strides away from you.
-Effect Stride up to your Speed toward it. This does not provoke reactions from your prey.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Trigger</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Your prey Moves away from you.
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Effect</t>
+          </r>
+          <r>
+            <t xml:space="preserve"> Move up to your Speed toward it. This does not provoke Reactions from your prey.</t>
+          </r>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Hunter's Aim ◆◆</t>
+          <t>Hunter's Aim ❷</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1614,21 +1760,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Mark Prey</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Make a weapon Strike against your Marked Prey. On this Strike, you gain a +2 circumstance bonus to the attack roll and ignore your prey's concealed condition and any lesser cover.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>Make a Deliberate weapon Strike ❷ against your Marked Prey. On this Strike, you gain a +2 Situation bonus to the attack roll and ignore your prey's concealed condition and any lesser cover.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1730,20 +1876,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You become Trained in Athletics.
 You gain the Weapon Familiarity Talent for free.
 Choose one Weapon Group in which you are Familiar. When making attacks with weapons of that Group, treat your Weapons Proficiency Bonus as 2 higher. This does not actually increase your Proficiency Rank and does not satisfy Expert, Master, or Legendary prerequisites.
-You may take the Reactive Strike Talent, ignoring its requirements. However, you may still only use Reactive Strike ↺ with weapons in which you are at least Expert Proficiency Rank.
+You may take the Reactive Strike Talent, even if you are not Expert in Melee. However, you may still only use Reactive Strike with weapons in which you are at least Expert Proficiency Rank.
 Every Talent in this Constellation requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>Weapon Group</t>
@@ -1766,21 +1912,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Drilled</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Your Reactive Strike ↺ also triggers when a creature within your reach uses a Move action.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>Your Intercept also triggers when a creature within your Reach uses any Motion Maneuver, whether or not it leaves your Reach.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1793,21 +1939,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Drilled</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Your Reactive Strike disrupts the triggering action on a Hit, if the Zone struck was Exposed.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>Your Intercept disrupts the triggering Maneuver on a Hit, not only a Critical Hit, if the Zone struck was Exposed.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1820,21 +1966,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Drilled</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Your weapon specialization damage arrives one rank early with your Drilled group: +2 while Trained, +3 at Expert, +4 at Master, +5 at Legendary.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1847,21 +1993,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Drilled</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>When a Graze would Expose one of your Zones, you may take 1 damage per level and Expose nothing instead.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>When one of your Strikes is Stopped and would Expose you, you may take 1 Vigor damage per level and Expose nothing instead.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/callings.xlsx
+++ b/data/callings.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4590" yWindow="4590" windowWidth="36450" windowHeight="13980" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,14 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weaponmaster" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,9 +30,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -45,7 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E5F6B"/>
+        <fgColor rgb="FF0E5F6B"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +76,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -477,7 +482,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Ambusher</t>
@@ -509,7 +514,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Berserker</t>
@@ -541,7 +546,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Bravo</t>
@@ -573,7 +578,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Hunter</t>
@@ -605,7 +610,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Weaponmaster</t>
@@ -648,14 +653,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -708,8 +711,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Sneak Attack</t>
@@ -766,7 +774,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Opportunist ❶↺</t>
@@ -796,6 +804,13 @@
             <t>Trigger</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> An ally Hits a creature within your reach.
 </t>
           </r>
@@ -808,6 +823,13 @@
             <t>Effect</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Strike that creature. It is Off-Guard to this Strike.</t>
           </r>
         </is>
@@ -815,7 +837,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Twist the Blade</t>
@@ -842,7 +864,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Bleeding Wound</t>
@@ -869,7 +891,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Unbalancing Blow</t>
@@ -907,14 +929,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -967,8 +987,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Rage ❶</t>
@@ -996,23 +1021,10 @@
           </r>
           <r>
             <rPr>
-              <rFont val="Calibri"/>
               <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Rage ❶</t>
-          </r>
-          <r>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Duration</t>
+            </rPr>
+            <t>Rage ❶
+Duration</t>
           </r>
           <r>
             <t xml:space="preserve"> 10 rounds
@@ -1026,7 +1038,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Sudden Charge ❷</t>
@@ -1060,6 +1072,13 @@
             <t>Sudden Charge ❷</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve">
 Move twice, then Quick Strike. Your Moves may provoke Intercepts as normal.</t>
           </r>
@@ -1068,7 +1087,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Thick Hide</t>
@@ -1095,7 +1114,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Blood in the Water</t>
@@ -1122,7 +1141,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Deaf to Pain</t>
@@ -1149,7 +1168,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Moment of Clarity ⓿</t>
@@ -1179,6 +1198,13 @@
             <t>Frequency</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> once per encounter
 You push back your rage for a moment in order to think clearly. Until the end of this round, you lose your Heedless condition.</t>
           </r>
@@ -1202,14 +1228,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1262,8 +1286,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="135" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Panache</t>
@@ -1294,7 +1323,7 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Finisher ❶</t>
@@ -1328,6 +1357,13 @@
             <t>Hit</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> add 2d6 precision damage.
 </t>
           </r>
@@ -1340,6 +1376,13 @@
             <t>Graze</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> add 1d6 precision damage.
 You lose the Panache either way.</t>
           </r>
@@ -1348,7 +1391,7 @@
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Opportune Parry ⓿↺</t>
@@ -1378,6 +1421,13 @@
             <t>Trigger</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> A creature's Strike against you is Stopped (a Graze or a Miss) while you have Panache.
 </t>
           </r>
@@ -1390,6 +1440,13 @@
             <t>Effect</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You take Control of the attacking weapon as though you had Parried, without spending an action.</t>
           </r>
         </is>
@@ -1451,7 +1508,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Elegant Buckler</t>
@@ -1479,7 +1536,7 @@
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
     </row>
-    <row r="8">
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Extravagant Parry ❶</t>
@@ -1509,6 +1566,13 @@
             <t>Requirements</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> You're wielding one or more one-handed weapons
 You gain a +1 Situation bonus to Guard until your next Opportunity, or a +2 Situation bonus if you have a free hand or are wielding a weapon with the parry trait. You lose this Situation bonus if you no longer meet this feat's requirement. If a creature misses you with a Strike while you have this bonus, you gain panache.</t>
           </r>
@@ -1528,14 +1592,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -1588,8 +1650,13 @@
           <t>Grants (restricted TPs this talent gives)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Mark Prey ❶</t>
@@ -1673,7 +1740,7 @@
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Hobbling Strike</t>
@@ -1700,7 +1767,7 @@
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>No Escape ❶↺</t>
@@ -1730,6 +1797,13 @@
             <t>Trigger</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Your prey Moves away from you.
 </t>
           </r>
@@ -1742,6 +1816,13 @@
             <t>Effect</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <family val="2"/>
+              <color theme="1"/>
+              <sz val="11"/>
+              <scheme val="minor"/>
+            </rPr>
             <t xml:space="preserve"> Move up to your Speed toward it. This does not provoke Reactions from your prey.</t>
           </r>
         </is>
@@ -1749,7 +1830,7 @@
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Hunter's Aim ❷</t>
@@ -1787,20 +1868,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="2" max="3"/>
+    <col width="26" customWidth="1" min="4" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="10" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1859,8 +1937,13 @@
           <t>Free Talent (handed over, no point spent)</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="120" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Drilled</t>
@@ -1900,8 +1983,13 @@
           <t>Weapon Familiarity</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Hold the Line</t>
@@ -1927,8 +2015,13 @@
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
-    </row>
-    <row r="4">
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Punishing Blow</t>
@@ -1954,8 +2047,13 @@
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
-    </row>
-    <row r="5">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Second Nature</t>
@@ -1981,8 +2079,13 @@
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
-    </row>
-    <row r="6">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Hold Fast</t>
@@ -2008,6 +2111,11 @@
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/callings.xlsx
+++ b/data/callings.xlsx
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -714,6 +716,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -929,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -939,6 +946,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -990,6 +999,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1238,6 +1252,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1289,6 +1305,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1602,6 +1623,8 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1655,6 +1678,11 @@
           <t>Enabled?</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -1685,6 +1713,11 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>60 ft</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1868,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1912,8 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1940,6 +1975,11 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Enabled?</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>

--- a/data/callings.xlsx
+++ b/data/callings.xlsx
@@ -1043,8 +1043,8 @@
           <r>
             <t xml:space="preserve"> 10 rounds
 You gain Temporary Vigor = level + Might, +2 melee damage, −1 Evade. While raging, you are Heedless.
-Afterward, you're fatigued until you spend three actions to catch your breath.
-You may end your Rage as a free action, becoming fatigued as though it had run its course.
+Afterward, increase your Fatigued by 1 until you spend three actions to catch your breath.
+You may end your Rage as a free action, increasing your Fatigued by 1 as though it had run its course.
 Damage bonus rises to +4 melee damage at Expert rank, +6 at Master, +8 at Legendary.</t>
           </r>
         </is>
